--- a/datos/estadisticas.xlsx
+++ b/datos/estadisticas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>vehiculo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>electrolinera</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bateria_al_recargar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>numero_recorrido</t>
         </is>
@@ -453,37 +441,595 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BMW i4 eDrive40</t>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.2</v>
+        <v>19.8</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nissan LEAF Standard Range 52 kWh</t>
+          <t>BMW i4 eDrive40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CC Cacique</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CC Cacique</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Homecenter</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Éxito de la Rosita</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Éxito de la Rosita</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CC Cacique</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>19.1</v>
       </c>
-      <c r="D3" t="n">
-        <v>26</v>
+      <c r="D25" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/datos/estadisticas.xlsx
+++ b/datos/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,14 +446,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.8</v>
+        <v>16.3</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -464,14 +464,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Promotores del Oriente</t>
+          <t>CC Quinta Etapa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.7</v>
+        <v>19.5</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -482,14 +482,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Promotores del Oriente</t>
+          <t>CC Cacique</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13.2</v>
+        <v>17.7</v>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -500,14 +500,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -518,14 +518,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.7</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.3</v>
+        <v>19.6</v>
       </c>
       <c r="D7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -554,14 +554,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CC Cacique</t>
+          <t>CC Quinta Etapa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="D8" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9">
@@ -572,14 +572,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Promotores del Oriente</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.9</v>
+        <v>16.4</v>
       </c>
       <c r="D9" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -590,14 +590,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.3</v>
+        <v>17.5</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.1</v>
+        <v>19.7</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -644,14 +644,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19.9</v>
+        <v>18.1</v>
       </c>
       <c r="D13" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
@@ -662,14 +662,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Éxito de la Rosita</t>
+          <t>CC Cacique</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="D14" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.8</v>
+        <v>16.4</v>
       </c>
       <c r="D15" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">
@@ -698,14 +698,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Éxito de la Rosita</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
@@ -716,50 +716,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Promotores del Oriente</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="D17" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BMW i4 eDrive40</t>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="D18" t="n">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nissan LEAF Standard Range 52 kWh</t>
+          <t>BMW i4 eDrive40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>Promotores del Oriente</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="D19" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20">
@@ -770,14 +770,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>CC Cacique</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="D20" t="n">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21">
@@ -788,14 +788,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19.4</v>
+        <v>17.8</v>
       </c>
       <c r="D21" t="n">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22">
@@ -806,14 +806,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CC Cacique</t>
+          <t>Promotores del Oriente</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="D22" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23">
@@ -824,14 +824,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="D23" t="n">
-        <v>341</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24">
@@ -842,14 +842,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="D24" t="n">
-        <v>345</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25">
@@ -860,14 +860,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Promotores del Oriente</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>19.1</v>
+        <v>18.5</v>
       </c>
       <c r="D25" t="n">
-        <v>363</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26">
@@ -878,14 +878,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="D26" t="n">
-        <v>381</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27">
@@ -896,14 +896,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="D27" t="n">
-        <v>387</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28">
@@ -914,14 +914,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>16.7</v>
       </c>
       <c r="D28" t="n">
-        <v>411</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29">
@@ -932,14 +932,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="D29" t="n">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30">
@@ -950,14 +950,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.3</v>
+        <v>19.2</v>
       </c>
       <c r="D30" t="n">
-        <v>440</v>
+        <v>421</v>
       </c>
     </row>
     <row r="31">
@@ -968,14 +968,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="D31" t="n">
-        <v>455</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32">
@@ -986,14 +986,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>CC Cacique</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>18.2</v>
+        <v>19.5</v>
       </c>
       <c r="D32" t="n">
-        <v>462</v>
+        <v>444</v>
       </c>
     </row>
     <row r="33">
@@ -1004,14 +1004,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>Promotores del Oriente</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17</v>
+        <v>19.4</v>
       </c>
       <c r="D33" t="n">
-        <v>484</v>
+        <v>472</v>
       </c>
     </row>
     <row r="34">
@@ -1022,14 +1022,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>18.1</v>
+        <v>17.2</v>
       </c>
       <c r="D34" t="n">
-        <v>490</v>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/datos/estadisticas.xlsx
+++ b/datos/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,14 +446,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.3</v>
+        <v>19.5</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -464,14 +464,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>CC Cacique</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -482,14 +482,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CC Cacique</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -500,14 +500,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>CC Cacique</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.3</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -518,14 +518,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Éxito de la Rosita</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>19.4</v>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -536,14 +536,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CC Cacique</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.6</v>
+        <v>17.4</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -554,14 +554,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CC Quinta Etapa</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.3</v>
+        <v>16.9</v>
       </c>
       <c r="D8" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
@@ -572,14 +572,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>CC Quinta Etapa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.4</v>
+        <v>19.3</v>
       </c>
       <c r="D9" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -590,14 +590,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>Promotores del Oriente</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18.5</v>
+        <v>14.3</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -608,14 +608,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.5</v>
+        <v>19.9</v>
       </c>
       <c r="D11" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -626,14 +626,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.7</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -644,14 +644,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="D13" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14">
@@ -662,14 +662,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CC Cacique</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.3</v>
+        <v>18.3</v>
       </c>
       <c r="D14" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15">
@@ -680,14 +680,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="D15" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16">
@@ -698,14 +698,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nissan LEAF Standard Range 52 kWh</t>
+          <t>BMW i4 eDrive40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Éxito de la Rosita</t>
+          <t>Promotores del Oriente</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.7</v>
+        <v>18.7</v>
       </c>
       <c r="D18" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BMW i4 eDrive40</t>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="D19" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20">
@@ -770,14 +770,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CC Cacique</t>
+          <t>Promotores del Oriente</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="D20" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21">
@@ -788,14 +788,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Éxito de la Rosita</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="D21" t="n">
-        <v>291</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="D22" t="n">
-        <v>297</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23">
@@ -824,14 +824,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EDS Terpel Piedecuesta</t>
+          <t>CC Quinta Etapa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.7</v>
+        <v>19.2</v>
       </c>
       <c r="D23" t="n">
-        <v>320</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24">
@@ -842,14 +842,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Éxito de la Rosita</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>19.4</v>
+        <v>16.8</v>
       </c>
       <c r="D24" t="n">
-        <v>326</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25">
@@ -860,14 +860,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="D25" t="n">
-        <v>344</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26">
@@ -878,14 +878,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>CC Quinta Etapa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>19.9</v>
+        <v>18.1</v>
       </c>
       <c r="D26" t="n">
-        <v>368</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19.7</v>
+        <v>19.2</v>
       </c>
       <c r="D27" t="n">
-        <v>372</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.7</v>
+        <v>15.2</v>
       </c>
       <c r="D28" t="n">
-        <v>395</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29">
@@ -932,14 +932,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CC la Florida</t>
+          <t>Homecenter</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
       <c r="D29" t="n">
-        <v>405</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30">
@@ -950,14 +950,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>CC la Florida</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="D30" t="n">
-        <v>421</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31">
@@ -968,14 +968,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="D31" t="n">
-        <v>443</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32">
@@ -986,14 +986,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CC Cacique</t>
+          <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="D32" t="n">
-        <v>444</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33">
@@ -1004,14 +1004,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Promotores del Oriente</t>
+          <t>Éxito de la Rosita</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="D33" t="n">
-        <v>472</v>
+        <v>495</v>
       </c>
     </row>
     <row r="34">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Homecenter</t>
+          <t>CC Quinta Etapa</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>18.3</v>
       </c>
       <c r="D34" t="n">
-        <v>483</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35">
@@ -1040,14 +1040,608 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>CC Cacique</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Homecenter</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="D35" t="n">
-        <v>494</v>
+      <c r="C39" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D45" t="n">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D48" t="n">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CC Cacique</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Éxito de la Rosita</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D51" t="n">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>18</v>
+      </c>
+      <c r="D52" t="n">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D65" t="n">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D67" t="n">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/datos/estadisticas.xlsx
+++ b/datos/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,14 +446,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Éxito de la Rosita</t>
+          <t>CC Cacique</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -464,14 +464,554 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>EDS Terpel Piedecuesta</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>16.9</v>
       </c>
-      <c r="D3" t="n">
-        <v>45</v>
+      <c r="D11" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CC Quinta Etapa</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CC Cacique</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EDS Terpel Piedecuesta</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Homecenter</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Promotores del Oriente</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Éxito de la Rosita</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BMW i4 eDrive40</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CC Cacique</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nissan LEAF Standard Range 52 kWh</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CC la Florida</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" t="n">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
